--- a/tests/test_execution_log.xlsx
+++ b/tests/test_execution_log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/870353eac95c0052/!Tananyagok/Vizsgaremek/tanfolyamok/tests/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\13DAndorferVendel\tan\Tanfolyamok\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{C2AD54E7-76E1-4F29-8FA8-8976AAFED998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81AFEE8B-F48E-4709-B3D3-109111DAD74A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A4C3F6-3BFB-4528-A134-8BE8189EFB93}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24480" windowHeight="15480" activeTab="1" xr2:uid="{9519D7D8-28D4-43CB-8C88-C5098B5EED9B}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="62">
   <si>
     <t>Teszt ID</t>
   </si>
@@ -204,13 +204,16 @@
   </si>
   <si>
     <t>ADM_TC_027  Kijelentkezés - Sikeres kijelentkezés a jelentkezok.html oldalról</t>
+  </si>
+  <si>
+    <t>Babai Máté</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1106,16 +1109,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C543CF4-4989-4EC7-9909-0EE7D5094B92}">
   <dimension ref="A1:D28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="81.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="81.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1123,7 +1126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1131,7 +1134,7 @@
         <v>45797</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1156,7 +1159,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1167,7 +1170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1178,7 +1181,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -1189,7 +1192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1211,7 +1214,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1222,7 +1225,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1233,7 +1236,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -1255,7 +1258,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1266,7 +1269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1310,7 +1313,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1321,7 +1324,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1332,7 +1335,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -1343,7 +1346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1354,7 +1357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>28</v>
       </c>
@@ -1365,7 +1368,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>29</v>
       </c>
@@ -1376,7 +1379,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>30</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>31</v>
       </c>
@@ -1398,7 +1401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>32</v>
       </c>
@@ -1417,16 +1420,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6436B23-F6DD-4C4F-BB92-ED0D4F4A9B94}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="80.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" customWidth="1"/>
+    <col min="1" max="1" width="80.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
+    <col min="4" max="4" width="14.125" customWidth="1"/>
+    <col min="5" max="5" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1434,15 +1437,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="1">
-        <v>45797</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>45708</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1456,309 +1459,309 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>40</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>41</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
         <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>47</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3">
       <c r="A23" t="s">
         <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3">
       <c r="A24" t="s">
         <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3">
       <c r="A25" t="s">
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3">
       <c r="A26" t="s">
         <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3">
       <c r="A30" t="s">
         <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3">
       <c r="A31" t="s">
         <v>59</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3">
       <c r="A32" t="s">
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
